--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="24217996"/>
-        <c:axId val="76228803"/>
+        <c:axId val="6665506"/>
+        <c:axId val="11392902"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="24217996"/>
+        <c:axId val="6665506"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76228803"/>
+        <c:crossAx val="11392902"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76228803"/>
+        <c:axId val="11392902"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24217996"/>
+        <c:crossAx val="6665506"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32032527"/>
-        <c:axId val="86130147"/>
+        <c:axId val="17625886"/>
+        <c:axId val="45784829"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32032527"/>
+        <c:axId val="17625886"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86130147"/>
+        <c:crossAx val="45784829"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86130147"/>
+        <c:axId val="45784829"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32032527"/>
+        <c:crossAx val="17625886"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="56281559"/>
-        <c:axId val="68748454"/>
+        <c:axId val="55453798"/>
+        <c:axId val="6835817"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56281559"/>
+        <c:axId val="55453798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68748454"/>
+        <c:crossAx val="6835817"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68748454"/>
+        <c:axId val="6835817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56281559"/>
+        <c:crossAx val="55453798"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19870192"/>
-        <c:axId val="73171282"/>
+        <c:axId val="63509903"/>
+        <c:axId val="76397339"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19870192"/>
+        <c:axId val="63509903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73171282"/>
+        <c:crossAx val="76397339"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73171282"/>
+        <c:axId val="76397339"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19870192"/>
+        <c:crossAx val="63509903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54312491"/>
-        <c:axId val="90252411"/>
+        <c:axId val="97570060"/>
+        <c:axId val="74248808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54312491"/>
+        <c:axId val="97570060"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90252411"/>
+        <c:crossAx val="74248808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90252411"/>
+        <c:axId val="74248808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54312491"/>
+        <c:crossAx val="97570060"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74386707"/>
-        <c:axId val="29459953"/>
+        <c:axId val="2973012"/>
+        <c:axId val="44291716"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74386707"/>
+        <c:axId val="2973012"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29459953"/>
+        <c:crossAx val="44291716"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29459953"/>
+        <c:axId val="44291716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74386707"/>
+        <c:crossAx val="2973012"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="6665506"/>
-        <c:axId val="11392902"/>
+        <c:axId val="79507874"/>
+        <c:axId val="22852945"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="6665506"/>
+        <c:axId val="79507874"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11392902"/>
+        <c:crossAx val="22852945"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11392902"/>
+        <c:axId val="22852945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6665506"/>
+        <c:crossAx val="79507874"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17625886"/>
-        <c:axId val="45784829"/>
+        <c:axId val="70145618"/>
+        <c:axId val="77959666"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17625886"/>
+        <c:axId val="70145618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45784829"/>
+        <c:crossAx val="77959666"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45784829"/>
+        <c:axId val="77959666"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17625886"/>
+        <c:crossAx val="70145618"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="55453798"/>
-        <c:axId val="6835817"/>
+        <c:axId val="98554860"/>
+        <c:axId val="54423133"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55453798"/>
+        <c:axId val="98554860"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6835817"/>
+        <c:crossAx val="54423133"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6835817"/>
+        <c:axId val="54423133"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55453798"/>
+        <c:crossAx val="98554860"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="63509903"/>
-        <c:axId val="76397339"/>
+        <c:axId val="67698736"/>
+        <c:axId val="94100958"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63509903"/>
+        <c:axId val="67698736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76397339"/>
+        <c:crossAx val="94100958"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76397339"/>
+        <c:axId val="94100958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63509903"/>
+        <c:crossAx val="67698736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97570060"/>
-        <c:axId val="74248808"/>
+        <c:axId val="14411340"/>
+        <c:axId val="3289204"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97570060"/>
+        <c:axId val="14411340"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74248808"/>
+        <c:crossAx val="3289204"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74248808"/>
+        <c:axId val="3289204"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97570060"/>
+        <c:crossAx val="14411340"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="2973012"/>
-        <c:axId val="44291716"/>
+        <c:axId val="19598522"/>
+        <c:axId val="16185674"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2973012"/>
+        <c:axId val="19598522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44291716"/>
+        <c:crossAx val="16185674"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44291716"/>
+        <c:axId val="16185674"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2973012"/>
+        <c:crossAx val="19598522"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Band: Nascent</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 – &lt;1.8</t>
+    <t xml:space="preserve">1.0 – &lt;1.5</t>
   </si>
   <si>
     <t xml:space="preserve">Half-open bands; a pillar band in parentheses means judged, gap and held rows outnumber the levelled measured and documented ones.</t>
@@ -201,25 +201,25 @@
     <t xml:space="preserve">Band: Emerging</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8 – &lt;2.6</t>
+    <t xml:space="preserve">1.5 – &lt;2.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Established</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6 – &lt;3.4</t>
+    <t xml:space="preserve">2.5 – &lt;3.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Advanced</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4 – &lt;4.2</t>
+    <t xml:space="preserve">3.5 – &lt;4.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Transformative</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 – 5.0</t>
+    <t xml:space="preserve">4.5 – 5.0</t>
   </si>
   <si>
     <t xml:space="preserve">Universal prerequisites</t>
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="79507874"/>
-        <c:axId val="22852945"/>
+        <c:axId val="94229051"/>
+        <c:axId val="54108090"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="79507874"/>
+        <c:axId val="94229051"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22852945"/>
+        <c:crossAx val="54108090"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22852945"/>
+        <c:axId val="54108090"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79507874"/>
+        <c:crossAx val="94229051"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70145618"/>
-        <c:axId val="77959666"/>
+        <c:axId val="26196226"/>
+        <c:axId val="65282118"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70145618"/>
+        <c:axId val="26196226"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77959666"/>
+        <c:crossAx val="65282118"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77959666"/>
+        <c:axId val="65282118"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70145618"/>
+        <c:crossAx val="26196226"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="98554860"/>
-        <c:axId val="54423133"/>
+        <c:axId val="75952170"/>
+        <c:axId val="35776839"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="98554860"/>
+        <c:axId val="75952170"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54423133"/>
+        <c:crossAx val="35776839"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54423133"/>
+        <c:axId val="35776839"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98554860"/>
+        <c:crossAx val="75952170"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="67698736"/>
-        <c:axId val="94100958"/>
+        <c:axId val="58997114"/>
+        <c:axId val="54256986"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67698736"/>
+        <c:axId val="58997114"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94100958"/>
+        <c:crossAx val="54256986"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94100958"/>
+        <c:axId val="54256986"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67698736"/>
+        <c:crossAx val="58997114"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14411340"/>
-        <c:axId val="3289204"/>
+        <c:axId val="4391378"/>
+        <c:axId val="94688096"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14411340"/>
+        <c:axId val="4391378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3289204"/>
+        <c:crossAx val="94688096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3289204"/>
+        <c:axId val="94688096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14411340"/>
+        <c:crossAx val="4391378"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19598522"/>
-        <c:axId val="16185674"/>
+        <c:axId val="94724754"/>
+        <c:axId val="77438639"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19598522"/>
+        <c:axId val="94724754"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16185674"/>
+        <c:crossAx val="77438639"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16185674"/>
+        <c:axId val="77438639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19598522"/>
+        <c:crossAx val="94724754"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10271,7 +10271,7 @@
         <v/>
       </c>
       <c r="E66" s="9" t="str">
-        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F66" s="15" t="n">
@@ -10316,7 +10316,7 @@
         <v/>
       </c>
       <c r="E67" s="9" t="str">
-        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F67" s="15" t="n">
@@ -10361,7 +10361,7 @@
         <v/>
       </c>
       <c r="E68" s="9" t="str">
-        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F68" s="15" t="n">
@@ -10406,7 +10406,7 @@
         <v/>
       </c>
       <c r="E69" s="9" t="str">
-        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F69" s="15" t="n">
@@ -10451,7 +10451,7 @@
         <v/>
       </c>
       <c r="E70" s="9" t="str">
-        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F70" s="15" t="n">
@@ -10496,7 +10496,7 @@
         <v/>
       </c>
       <c r="E71" s="9" t="str">
-        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F71" s="15" t="n">
@@ -10541,7 +10541,7 @@
         <v/>
       </c>
       <c r="E72" s="9" t="str">
-        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Not rated</v>
       </c>
       <c r="F72" s="15" t="n">

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -180,7 +180,7 @@
     <t xml:space="preserve">Readiness threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial.</t>
+    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial. Set to the Established band's lower edge.</t>
   </si>
   <si>
     <t xml:space="preserve">Leapfrog threshold</t>
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="94229051"/>
-        <c:axId val="54108090"/>
+        <c:axId val="20159978"/>
+        <c:axId val="30998820"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="94229051"/>
+        <c:axId val="20159978"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54108090"/>
+        <c:crossAx val="30998820"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54108090"/>
+        <c:axId val="30998820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94229051"/>
+        <c:crossAx val="20159978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26196226"/>
-        <c:axId val="65282118"/>
+        <c:axId val="5466313"/>
+        <c:axId val="24344764"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26196226"/>
+        <c:axId val="5466313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65282118"/>
+        <c:crossAx val="24344764"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65282118"/>
+        <c:axId val="24344764"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26196226"/>
+        <c:crossAx val="5466313"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="75952170"/>
-        <c:axId val="35776839"/>
+        <c:axId val="59956577"/>
+        <c:axId val="31844982"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75952170"/>
+        <c:axId val="59956577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35776839"/>
+        <c:crossAx val="31844982"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35776839"/>
+        <c:axId val="31844982"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75952170"/>
+        <c:crossAx val="59956577"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58997114"/>
-        <c:axId val="54256986"/>
+        <c:axId val="86308501"/>
+        <c:axId val="51377132"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58997114"/>
+        <c:axId val="86308501"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54256986"/>
+        <c:crossAx val="51377132"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54256986"/>
+        <c:axId val="51377132"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58997114"/>
+        <c:crossAx val="86308501"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="4391378"/>
-        <c:axId val="94688096"/>
+        <c:axId val="6937599"/>
+        <c:axId val="66260260"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4391378"/>
+        <c:axId val="6937599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94688096"/>
+        <c:crossAx val="66260260"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94688096"/>
+        <c:axId val="66260260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4391378"/>
+        <c:crossAx val="6937599"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94724754"/>
-        <c:axId val="77438639"/>
+        <c:axId val="83071461"/>
+        <c:axId val="89096694"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94724754"/>
+        <c:axId val="83071461"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77438639"/>
+        <c:crossAx val="89096694"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77438639"/>
+        <c:axId val="89096694"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94724754"/>
+        <c:crossAx val="83071461"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5617,7 +5617,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>47</v>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -1014,7 +1014,7 @@
     <t xml:space="preserve">Use case area</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean of bearing indicators</t>
+    <t xml:space="preserve">Mean of enabling indicators</t>
   </si>
   <si>
     <t xml:space="preserve">Blocking / limiting factor</t>
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="20159978"/>
-        <c:axId val="30998820"/>
+        <c:axId val="39370468"/>
+        <c:axId val="72258287"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="20159978"/>
+        <c:axId val="39370468"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30998820"/>
+        <c:crossAx val="72258287"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30998820"/>
+        <c:axId val="72258287"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20159978"/>
+        <c:crossAx val="39370468"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5466313"/>
-        <c:axId val="24344764"/>
+        <c:axId val="43748300"/>
+        <c:axId val="2665020"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5466313"/>
+        <c:axId val="43748300"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24344764"/>
+        <c:crossAx val="2665020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24344764"/>
+        <c:axId val="2665020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5466313"/>
+        <c:crossAx val="43748300"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="59956577"/>
-        <c:axId val="31844982"/>
+        <c:axId val="24553417"/>
+        <c:axId val="34071942"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59956577"/>
+        <c:axId val="24553417"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31844982"/>
+        <c:crossAx val="34071942"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31844982"/>
+        <c:axId val="34071942"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59956577"/>
+        <c:crossAx val="24553417"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="86308501"/>
-        <c:axId val="51377132"/>
+        <c:axId val="5397717"/>
+        <c:axId val="31323893"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86308501"/>
+        <c:axId val="5397717"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51377132"/>
+        <c:crossAx val="31323893"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51377132"/>
+        <c:axId val="31323893"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86308501"/>
+        <c:crossAx val="5397717"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6937599"/>
-        <c:axId val="66260260"/>
+        <c:axId val="97565574"/>
+        <c:axId val="1296849"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6937599"/>
+        <c:axId val="97565574"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66260260"/>
+        <c:crossAx val="1296849"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66260260"/>
+        <c:axId val="1296849"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6937599"/>
+        <c:crossAx val="97565574"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83071461"/>
-        <c:axId val="89096694"/>
+        <c:axId val="47359273"/>
+        <c:axId val="82758710"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83071461"/>
+        <c:axId val="47359273"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89096694"/>
+        <c:crossAx val="82758710"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89096694"/>
+        <c:axId val="82758710"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83071461"/>
+        <c:crossAx val="47359273"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10858,7 +10858,7 @@
         <v>327</v>
       </c>
       <c r="B102" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(V$5:V$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,V$5:V$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C102" s="9" t="str">
@@ -10875,7 +10875,7 @@
         <v>328</v>
       </c>
       <c r="B103" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(W$5:W$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,W$5:W$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C103" s="9" t="str">
@@ -10892,7 +10892,7 @@
         <v>329</v>
       </c>
       <c r="B104" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(X$5:X$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,X$5:X$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C104" s="9" t="str">
@@ -10909,7 +10909,7 @@
         <v>330</v>
       </c>
       <c r="B105" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Y$5:Y$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Y$5:Y$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C105" s="9" t="str">
@@ -10926,7 +10926,7 @@
         <v>331</v>
       </c>
       <c r="B106" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Z$5:Z$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Z$5:Z$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C106" s="9" t="str">
@@ -10943,7 +10943,7 @@
         <v>332</v>
       </c>
       <c r="B107" s="15" t="str">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(AA$5:AA$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,AA$5:AA$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v/>
       </c>
       <c r="C107" s="9" t="str">

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Blank-Template.xlsx
@@ -234,10 +234,10 @@
     <t xml:space="preserve">AI-enabled services</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12 binds AGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruling pending ratification: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
+    <t xml:space="preserve">7.12 binds ADV, SMF, FIN, AGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruling 13.4: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
   </si>
   <si>
     <t xml:space="preserve">The shared ladder — scoring an indicator that is not a measurement</t>
@@ -876,7 +876,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">UC:AI</t>
+    <t xml:space="preserve">UC:ADV,SMF,FIN,AGI</t>
   </si>
   <si>
     <t xml:space="preserve">8.2</t>
@@ -1005,7 +1005,7 @@
     <t xml:space="preserve">Use case: ADV</t>
   </si>
   <si>
-    <t xml:space="preserve">Use case: AI-enabled (binds AGI)</t>
+    <t xml:space="preserve">Use case: personal or farm-level data (ADV, SMF, FIN, AGI)</t>
   </si>
   <si>
     <t xml:space="preserve">Use-case readiness  (feeds Playbook Step 2B — Digital Readiness)</t>
@@ -1622,11 +1622,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="39370468"/>
-        <c:axId val="72258287"/>
+        <c:axId val="77480436"/>
+        <c:axId val="53340811"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="39370468"/>
+        <c:axId val="77480436"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1656,7 +1656,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72258287"/>
+        <c:crossAx val="53340811"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1664,7 +1664,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72258287"/>
+        <c:axId val="53340811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -1709,7 +1709,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39370468"/>
+        <c:crossAx val="77480436"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1908,11 +1908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="43748300"/>
-        <c:axId val="2665020"/>
+        <c:axId val="72820978"/>
+        <c:axId val="7160998"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43748300"/>
+        <c:axId val="72820978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1945,7 +1945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2665020"/>
+        <c:crossAx val="7160998"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1953,7 +1953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2665020"/>
+        <c:axId val="7160998"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1996,7 +1996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43748300"/>
+        <c:crossAx val="72820978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2570,11 +2570,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="24553417"/>
-        <c:axId val="34071942"/>
+        <c:axId val="98699933"/>
+        <c:axId val="58817365"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24553417"/>
+        <c:axId val="98699933"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2607,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34071942"/>
+        <c:crossAx val="58817365"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2615,7 +2615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34071942"/>
+        <c:axId val="58817365"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24553417"/>
+        <c:crossAx val="98699933"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2848,11 +2848,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5397717"/>
-        <c:axId val="31323893"/>
+        <c:axId val="26579840"/>
+        <c:axId val="88392056"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5397717"/>
+        <c:axId val="26579840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2885,7 +2885,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31323893"/>
+        <c:crossAx val="88392056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2893,7 +2893,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31323893"/>
+        <c:axId val="88392056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2937,7 +2937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5397717"/>
+        <c:crossAx val="26579840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3145,11 +3145,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97565574"/>
-        <c:axId val="1296849"/>
+        <c:axId val="24503765"/>
+        <c:axId val="11354146"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97565574"/>
+        <c:axId val="24503765"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3182,7 +3182,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1296849"/>
+        <c:crossAx val="11354146"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3190,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1296849"/>
+        <c:axId val="11354146"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3233,7 +3233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97565574"/>
+        <c:crossAx val="24503765"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3513,11 +3513,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="47359273"/>
-        <c:axId val="82758710"/>
+        <c:axId val="62022675"/>
+        <c:axId val="74961196"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47359273"/>
+        <c:axId val="62022675"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3550,7 +3550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82758710"/>
+        <c:crossAx val="74961196"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3558,7 +3558,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82758710"/>
+        <c:axId val="74961196"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3601,7 +3601,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47359273"/>
+        <c:crossAx val="62022675"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10853,7 +10853,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
         <v>327</v>
       </c>
@@ -10862,12 +10862,12 @@
         <v/>
       </c>
       <c r="C102" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)",$D$97="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Unverified</v>
       </c>
       <c r="D102" s="10" t="str">
-        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1 2.9 4.1 5.5</v>
+        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 2.9 4.1 5.5 7.12</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10879,12 +10879,12 @@
         <v/>
       </c>
       <c r="C103" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$97="Present (narrow)"),$B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Unverified</v>
       </c>
       <c r="D103" s="10" t="str">
-        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1 2.9 4.1</v>
+        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 2.9 4.1 7.12</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10930,12 +10930,12 @@
         <v/>
       </c>
       <c r="C106" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)",$D$97="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Unverified</v>
       </c>
       <c r="D106" s="10" t="str">
-        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1 2.9 4.1 3.3 4.7 6.14</v>
+        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 2.9 4.1 3.3 4.7 6.14 7.12</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
